--- a/.helix/headers.xlsx
+++ b/.helix/headers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eds\mysite\.helix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7449985D-83EA-42E0-B301-6088B99085EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B954F02-EC88-46A0-B8F3-8E7B71D418A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,9 +30,6 @@
     <t>url</t>
   </si>
   <si>
-    <t>key</t>
-  </si>
-  <si>
     <t>value</t>
   </si>
   <si>
@@ -61,6 +58,9 @@
   </si>
   <si>
     <t>cms demo</t>
+  </si>
+  <si>
+    <t>header</t>
   </si>
 </sst>
 </file>
@@ -386,43 +386,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/.helix/headers.xlsx
+++ b/.helix/headers.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eds\mysite\.helix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B954F02-EC88-46A0-B8F3-8E7B71D418A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C939EF1-49A8-4760-BAB9-250B3BD3CAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="headers" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/.helix/headers.xlsx
+++ b/.helix/headers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eds\mysite\.helix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C939EF1-49A8-4760-BAB9-250B3BD3CAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41240715-8F8F-4B6E-B056-D8B2AE3B3154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,31 +36,31 @@
     <t>/**</t>
   </si>
   <si>
-    <t>author</t>
-  </si>
-  <si>
     <t>aem geeks</t>
   </si>
   <si>
     <t>/blocks/**</t>
   </si>
   <si>
-    <t>blocks</t>
-  </si>
-  <si>
     <t>custom blocks</t>
   </si>
   <si>
     <t>/cms/**</t>
   </si>
   <si>
-    <t>cms</t>
-  </si>
-  <si>
     <t>cms demo</t>
   </si>
   <si>
     <t>header</t>
+  </si>
+  <si>
+    <t>x-author</t>
+  </si>
+  <si>
+    <t>x-blocks</t>
+  </si>
+  <si>
+    <t>x-cms</t>
   </si>
 </sst>
 </file>
@@ -386,7 +386,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -397,32 +397,32 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
